--- a/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0001T0006Z000C1N123_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0001T0006Z000C1N123_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>23.66069109893436</v>
+        <v>3.844862303576833</v>
       </c>
       <c r="D2" t="n">
-        <v>28.0865893382014</v>
+        <v>4.564070767457729</v>
       </c>
       <c r="E2" t="n">
-        <v>10.79966882956413</v>
+        <v>1.754946184804171</v>
       </c>
       <c r="F2" t="n">
-        <v>10.15274678204618</v>
+        <v>1.649821352082505</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>39.12559049566084</v>
+        <v>6.357908455544887</v>
       </c>
       <c r="D3" t="n">
-        <v>38.85754163972178</v>
+        <v>6.314350516454789</v>
       </c>
       <c r="E3" t="n">
-        <v>10.79966882956413</v>
+        <v>1.754946184804171</v>
       </c>
       <c r="F3" t="n">
-        <v>10.15274678204618</v>
+        <v>1.649821352082505</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>27.68347370821241</v>
+        <v>4.498564477584518</v>
       </c>
       <c r="D4" t="n">
-        <v>27.77962585833349</v>
+        <v>4.514189201979192</v>
       </c>
       <c r="E4" t="n">
-        <v>10.79966882956413</v>
+        <v>1.754946184804171</v>
       </c>
       <c r="F4" t="n">
-        <v>10.15274678204618</v>
+        <v>1.649821352082505</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>22.48885990101038</v>
+        <v>3.654439733914187</v>
       </c>
       <c r="D5" t="n">
-        <v>22.67902987390181</v>
+        <v>3.685342354509045</v>
       </c>
       <c r="E5" t="n">
-        <v>10.79966882956413</v>
+        <v>1.754946184804171</v>
       </c>
       <c r="F5" t="n">
-        <v>10.15274678204618</v>
+        <v>1.649821352082505</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>50.88674937131551</v>
+        <v>8.26909677283877</v>
       </c>
       <c r="D6" t="n">
-        <v>51.04268443061579</v>
+        <v>8.294436219975065</v>
       </c>
       <c r="E6" t="n">
-        <v>10.79966882956413</v>
+        <v>1.754946184804171</v>
       </c>
       <c r="F6" t="n">
-        <v>10.15274678204618</v>
+        <v>1.649821352082505</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
